--- a/cashflow_templates/A_月次資金繰り表_12か月.xlsx
+++ b/cashflow_templates/A_月次資金繰り表_12か月.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="B2:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -613,26 +613,33 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>■ 未払金支払：経費の後払い分（カード払い・月末締め翌月払いの外注費・リース料など）の支払額を、実際に口座から出る月に入力します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>■ 科目名は自社に合わせて書き換えて構いません（A列）。行を挿入した場合は「計」の範囲を確認してください。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>入力セル（黄色・青字）</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>計算式セル（白・黒字）＝触らない</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>残高が「最低必要残高」を下回ると赤く表示されます</t>
         </is>
@@ -649,7 +656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -690,7 +697,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>46113</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="4">
@@ -780,47 +787,47 @@
         <v>2000000</v>
       </c>
       <c r="C8" s="14">
-        <f>B47</f>
+        <f>B48</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>C47</f>
+        <f>C48</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>D47</f>
+        <f>D48</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>E47</f>
+        <f>E48</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>F47</f>
+        <f>F48</f>
         <v/>
       </c>
       <c r="H8" s="14">
-        <f>G47</f>
+        <f>G48</f>
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>H47</f>
+        <f>H48</f>
         <v/>
       </c>
       <c r="J8" s="14">
-        <f>I47</f>
+        <f>I48</f>
         <v/>
       </c>
       <c r="K8" s="14">
-        <f>J47</f>
+        <f>J48</f>
         <v/>
       </c>
       <c r="L8" s="14">
-        <f>K47</f>
+        <f>K48</f>
         <v/>
       </c>
       <c r="M8" s="14">
-        <f>L47</f>
+        <f>L48</f>
         <v/>
       </c>
       <c r="N8" s="14">
@@ -1106,11 +1113,11 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜人件費（給与・賞与）</t>
+          <t xml:space="preserve">  支出｜未払金支払</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>900000</v>
+        <v>100000</v>
       </c>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="9" t="n"/>
@@ -1131,11 +1138,11 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜法定福利費</t>
+          <t xml:space="preserve">  支出｜人件費（給与・賞与）</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>130000</v>
+        <v>900000</v>
       </c>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
@@ -1156,11 +1163,11 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜地代家賃</t>
+          <t xml:space="preserve">  支出｜法定福利費</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>200000</v>
+        <v>130000</v>
       </c>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="9" t="n"/>
@@ -1181,11 +1188,11 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜水道光熱費・通信費</t>
+          <t xml:space="preserve">  支出｜地代家賃</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>60000</v>
+        <v>200000</v>
       </c>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="9" t="n"/>
@@ -1206,11 +1213,11 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜その他経費</t>
+          <t xml:space="preserve">  支出｜水道光熱費・通信費</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>180000</v>
+        <v>60000</v>
       </c>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
@@ -1231,11 +1238,11 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜支払利息・割引料</t>
+          <t xml:space="preserve">  支出｜その他経費</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>15000</v>
+        <v>180000</v>
       </c>
       <c r="C24" s="9" t="n"/>
       <c r="D24" s="9" t="n"/>
@@ -1254,170 +1261,172 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出｜支払利息・割引料</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+      <c r="L25" s="9" t="n"/>
+      <c r="M25" s="9" t="n"/>
+      <c r="N25" s="17">
+        <f>SUM(B25:M25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  支出 計</t>
         </is>
       </c>
-      <c r="B25" s="19">
-        <f>SUM(B16:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="19">
-        <f>SUM(C16:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="19">
-        <f>SUM(D16:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="19">
-        <f>SUM(E16:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="19">
-        <f>SUM(F16:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="19">
-        <f>SUM(G16:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="19">
-        <f>SUM(H16:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="19">
-        <f>SUM(I16:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="19">
-        <f>SUM(J16:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="19">
-        <f>SUM(K16:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="19">
-        <f>SUM(L16:L24)</f>
-        <v/>
-      </c>
-      <c r="M25" s="19">
-        <f>SUM(M16:M24)</f>
-        <v/>
-      </c>
-      <c r="N25" s="19">
-        <f>SUM(N16:N24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="B26" s="19">
+        <f>SUM(B16:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>SUM(C16:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>SUM(D16:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>SUM(E16:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>SUM(F16:F25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="19">
+        <f>SUM(G16:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
+        <f>SUM(H16:H25)</f>
+        <v/>
+      </c>
+      <c r="I26" s="19">
+        <f>SUM(I16:I25)</f>
+        <v/>
+      </c>
+      <c r="J26" s="19">
+        <f>SUM(J16:J25)</f>
+        <v/>
+      </c>
+      <c r="K26" s="19">
+        <f>SUM(K16:K25)</f>
+        <v/>
+      </c>
+      <c r="L26" s="19">
+        <f>SUM(L16:L25)</f>
+        <v/>
+      </c>
+      <c r="M26" s="19">
+        <f>SUM(M16:M25)</f>
+        <v/>
+      </c>
+      <c r="N26" s="19">
+        <f>SUM(N16:N25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>経常収支 差額（収入－支出）</t>
         </is>
       </c>
-      <c r="B26" s="14">
-        <f>B15-B25</f>
-        <v/>
-      </c>
-      <c r="C26" s="14">
-        <f>C15-C25</f>
-        <v/>
-      </c>
-      <c r="D26" s="14">
-        <f>D15-D25</f>
-        <v/>
-      </c>
-      <c r="E26" s="14">
-        <f>E15-E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="14">
-        <f>F15-F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="14">
-        <f>G15-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="14">
-        <f>H15-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="14">
-        <f>I15-I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="14">
-        <f>J15-J25</f>
-        <v/>
-      </c>
-      <c r="K26" s="14">
-        <f>K15-K25</f>
-        <v/>
-      </c>
-      <c r="L26" s="14">
-        <f>L15-L25</f>
-        <v/>
-      </c>
-      <c r="M26" s="14">
-        <f>M15-M25</f>
-        <v/>
-      </c>
-      <c r="N26" s="14">
-        <f>N15-N25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B27" s="14">
+        <f>B15-B26</f>
+        <v/>
+      </c>
+      <c r="C27" s="14">
+        <f>C15-C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="14">
+        <f>D15-D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>E15-E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>F15-F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>G15-G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>H15-H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>I15-I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="14">
+        <f>J15-J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="14">
+        <f>K15-K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="14">
+        <f>L15-L26</f>
+        <v/>
+      </c>
+      <c r="M27" s="14">
+        <f>M15-M26</f>
+        <v/>
+      </c>
+      <c r="N27" s="14">
+        <f>N15-N26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>経常外収支</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="16" t="n"/>
-      <c r="J27" s="16" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
-      <c r="M27" s="16" t="n"/>
-      <c r="N27" s="16" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入｜固定資産売却収入</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="17">
-        <f>SUM(B28:M28)</f>
-        <v/>
-      </c>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="16" t="n"/>
+      <c r="L28" s="16" t="n"/>
+      <c r="M28" s="16" t="n"/>
+      <c r="N28" s="16" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜保険金・補助金等</t>
+          <t xml:space="preserve">  収入｜固定資産売却収入</t>
         </is>
       </c>
       <c r="B29" s="9" t="n"/>
@@ -1440,7 +1449,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜その他</t>
+          <t xml:space="preserve">  収入｜保険金・補助金等</t>
         </is>
       </c>
       <c r="B30" s="9" t="n"/>
@@ -1461,96 +1470,94 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入｜その他</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="9" t="n"/>
+      <c r="M31" s="9" t="n"/>
+      <c r="N31" s="17">
+        <f>SUM(B31:M31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  収入 計</t>
         </is>
       </c>
-      <c r="B31" s="19">
-        <f>SUM(B28:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="19">
-        <f>SUM(C28:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="19">
-        <f>SUM(D28:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="19">
-        <f>SUM(E28:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="19">
-        <f>SUM(F28:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="19">
-        <f>SUM(G28:G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="19">
-        <f>SUM(H28:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="19">
-        <f>SUM(I28:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="19">
-        <f>SUM(J28:J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="19">
-        <f>SUM(K28:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="19">
-        <f>SUM(L28:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="19">
-        <f>SUM(M28:M30)</f>
-        <v/>
-      </c>
-      <c r="N31" s="19">
-        <f>SUM(N28:N30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  支出｜設備投資（固定資産購入）</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
-      <c r="L32" s="9" t="n"/>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="17">
-        <f>SUM(B32:M32)</f>
+      <c r="B32" s="19">
+        <f>SUM(B29:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="19">
+        <f>SUM(C29:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="19">
+        <f>SUM(D29:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="19">
+        <f>SUM(E29:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="19">
+        <f>SUM(F29:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="19">
+        <f>SUM(G29:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="19">
+        <f>SUM(H29:H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="19">
+        <f>SUM(I29:I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="19">
+        <f>SUM(J29:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="19">
+        <f>SUM(K29:K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="19">
+        <f>SUM(L29:L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="19">
+        <f>SUM(M29:M31)</f>
+        <v/>
+      </c>
+      <c r="N32" s="19">
+        <f>SUM(N29:N31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜法人税・消費税等納付</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>250000</v>
-      </c>
+          <t xml:space="preserve">  支出｜設備投資（固定資産購入）</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
@@ -1570,10 +1577,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜その他</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="n"/>
+          <t xml:space="preserve">  支出｜法人税・消費税等納付</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>250000</v>
+      </c>
       <c r="C34" s="9" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
@@ -1591,170 +1600,170 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出｜その他</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="17">
+        <f>SUM(B35:M35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  支出 計</t>
         </is>
       </c>
-      <c r="B35" s="19">
-        <f>SUM(B32:B34)</f>
-        <v/>
-      </c>
-      <c r="C35" s="19">
-        <f>SUM(C32:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="19">
-        <f>SUM(D32:D34)</f>
-        <v/>
-      </c>
-      <c r="E35" s="19">
-        <f>SUM(E32:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="19">
-        <f>SUM(F32:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="19">
-        <f>SUM(G32:G34)</f>
-        <v/>
-      </c>
-      <c r="H35" s="19">
-        <f>SUM(H32:H34)</f>
-        <v/>
-      </c>
-      <c r="I35" s="19">
-        <f>SUM(I32:I34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="19">
-        <f>SUM(J32:J34)</f>
-        <v/>
-      </c>
-      <c r="K35" s="19">
-        <f>SUM(K32:K34)</f>
-        <v/>
-      </c>
-      <c r="L35" s="19">
-        <f>SUM(L32:L34)</f>
-        <v/>
-      </c>
-      <c r="M35" s="19">
-        <f>SUM(M32:M34)</f>
-        <v/>
-      </c>
-      <c r="N35" s="19">
-        <f>SUM(N32:N34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="B36" s="19">
+        <f>SUM(B33:B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>SUM(C33:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>SUM(D33:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>SUM(E33:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>SUM(F33:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>SUM(G33:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>SUM(H33:H35)</f>
+        <v/>
+      </c>
+      <c r="I36" s="19">
+        <f>SUM(I33:I35)</f>
+        <v/>
+      </c>
+      <c r="J36" s="19">
+        <f>SUM(J33:J35)</f>
+        <v/>
+      </c>
+      <c r="K36" s="19">
+        <f>SUM(K33:K35)</f>
+        <v/>
+      </c>
+      <c r="L36" s="19">
+        <f>SUM(L33:L35)</f>
+        <v/>
+      </c>
+      <c r="M36" s="19">
+        <f>SUM(M33:M35)</f>
+        <v/>
+      </c>
+      <c r="N36" s="19">
+        <f>SUM(N33:N35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>経常外収支 差額（収入－支出）</t>
         </is>
       </c>
-      <c r="B36" s="14">
-        <f>B31-B35</f>
-        <v/>
-      </c>
-      <c r="C36" s="14">
-        <f>C31-C35</f>
-        <v/>
-      </c>
-      <c r="D36" s="14">
-        <f>D31-D35</f>
-        <v/>
-      </c>
-      <c r="E36" s="14">
-        <f>E31-E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="14">
-        <f>F31-F35</f>
-        <v/>
-      </c>
-      <c r="G36" s="14">
-        <f>G31-G35</f>
-        <v/>
-      </c>
-      <c r="H36" s="14">
-        <f>H31-H35</f>
-        <v/>
-      </c>
-      <c r="I36" s="14">
-        <f>I31-I35</f>
-        <v/>
-      </c>
-      <c r="J36" s="14">
-        <f>J31-J35</f>
-        <v/>
-      </c>
-      <c r="K36" s="14">
-        <f>K31-K35</f>
-        <v/>
-      </c>
-      <c r="L36" s="14">
-        <f>L31-L35</f>
-        <v/>
-      </c>
-      <c r="M36" s="14">
-        <f>M31-M35</f>
-        <v/>
-      </c>
-      <c r="N36" s="14">
-        <f>N31-N35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="B37" s="14">
+        <f>B32-B36</f>
+        <v/>
+      </c>
+      <c r="C37" s="14">
+        <f>C32-C36</f>
+        <v/>
+      </c>
+      <c r="D37" s="14">
+        <f>D32-D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="14">
+        <f>E32-E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="14">
+        <f>F32-F36</f>
+        <v/>
+      </c>
+      <c r="G37" s="14">
+        <f>G32-G36</f>
+        <v/>
+      </c>
+      <c r="H37" s="14">
+        <f>H32-H36</f>
+        <v/>
+      </c>
+      <c r="I37" s="14">
+        <f>I32-I36</f>
+        <v/>
+      </c>
+      <c r="J37" s="14">
+        <f>J32-J36</f>
+        <v/>
+      </c>
+      <c r="K37" s="14">
+        <f>K32-K36</f>
+        <v/>
+      </c>
+      <c r="L37" s="14">
+        <f>L32-L36</f>
+        <v/>
+      </c>
+      <c r="M37" s="14">
+        <f>M32-M36</f>
+        <v/>
+      </c>
+      <c r="N37" s="14">
+        <f>N32-N36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>財務収支</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="16" t="n"/>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
-      <c r="M37" s="16" t="n"/>
-      <c r="N37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  収入｜借入金</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="17">
-        <f>SUM(B38:M38)</f>
-        <v/>
-      </c>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="16" t="n"/>
+      <c r="H38" s="16" t="n"/>
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="16" t="n"/>
+      <c r="K38" s="16" t="n"/>
+      <c r="L38" s="16" t="n"/>
+      <c r="M38" s="16" t="n"/>
+      <c r="N38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜増資・出資</t>
+          <t xml:space="preserve">  収入｜借入金</t>
         </is>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -1777,7 +1786,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  収入｜その他</t>
+          <t xml:space="preserve">  収入｜増資・出資</t>
         </is>
       </c>
       <c r="B40" s="9" t="n"/>
@@ -1798,96 +1807,96 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  収入｜その他</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="9" t="n"/>
+      <c r="M41" s="9" t="n"/>
+      <c r="N41" s="17">
+        <f>SUM(B41:M41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  収入 計</t>
         </is>
       </c>
-      <c r="B41" s="19">
-        <f>SUM(B38:B40)</f>
-        <v/>
-      </c>
-      <c r="C41" s="19">
-        <f>SUM(C38:C40)</f>
-        <v/>
-      </c>
-      <c r="D41" s="19">
-        <f>SUM(D38:D40)</f>
-        <v/>
-      </c>
-      <c r="E41" s="19">
-        <f>SUM(E38:E40)</f>
-        <v/>
-      </c>
-      <c r="F41" s="19">
-        <f>SUM(F38:F40)</f>
-        <v/>
-      </c>
-      <c r="G41" s="19">
-        <f>SUM(G38:G40)</f>
-        <v/>
-      </c>
-      <c r="H41" s="19">
-        <f>SUM(H38:H40)</f>
-        <v/>
-      </c>
-      <c r="I41" s="19">
-        <f>SUM(I38:I40)</f>
-        <v/>
-      </c>
-      <c r="J41" s="19">
-        <f>SUM(J38:J40)</f>
-        <v/>
-      </c>
-      <c r="K41" s="19">
-        <f>SUM(K38:K40)</f>
-        <v/>
-      </c>
-      <c r="L41" s="19">
-        <f>SUM(L38:L40)</f>
-        <v/>
-      </c>
-      <c r="M41" s="19">
-        <f>SUM(M38:M40)</f>
-        <v/>
-      </c>
-      <c r="N41" s="19">
-        <f>SUM(N38:N40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  支出｜借入金返済</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="9" t="n"/>
-      <c r="M42" s="9" t="n"/>
-      <c r="N42" s="17">
-        <f>SUM(B42:M42)</f>
+      <c r="B42" s="19">
+        <f>SUM(B39:B41)</f>
+        <v/>
+      </c>
+      <c r="C42" s="19">
+        <f>SUM(C39:C41)</f>
+        <v/>
+      </c>
+      <c r="D42" s="19">
+        <f>SUM(D39:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="19">
+        <f>SUM(E39:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="19">
+        <f>SUM(F39:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="19">
+        <f>SUM(G39:G41)</f>
+        <v/>
+      </c>
+      <c r="H42" s="19">
+        <f>SUM(H39:H41)</f>
+        <v/>
+      </c>
+      <c r="I42" s="19">
+        <f>SUM(I39:I41)</f>
+        <v/>
+      </c>
+      <c r="J42" s="19">
+        <f>SUM(J39:J41)</f>
+        <v/>
+      </c>
+      <c r="K42" s="19">
+        <f>SUM(K39:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="19">
+        <f>SUM(L39:L41)</f>
+        <v/>
+      </c>
+      <c r="M42" s="19">
+        <f>SUM(M39:M41)</f>
+        <v/>
+      </c>
+      <c r="N42" s="19">
+        <f>SUM(N39:N41)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜配当金・役員借入返済</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="n"/>
+          <t xml:space="preserve">  支出｜借入金返済</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>150000</v>
+      </c>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
@@ -1907,7 +1916,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  支出｜その他</t>
+          <t xml:space="preserve">  支出｜配当金・役員借入返済</t>
         </is>
       </c>
       <c r="B44" s="9" t="n"/>
@@ -1928,248 +1937,271 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  支出｜その他</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="17">
+        <f>SUM(B45:M45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  支出 計</t>
         </is>
       </c>
-      <c r="B45" s="19">
-        <f>SUM(B42:B44)</f>
-        <v/>
-      </c>
-      <c r="C45" s="19">
-        <f>SUM(C42:C44)</f>
-        <v/>
-      </c>
-      <c r="D45" s="19">
-        <f>SUM(D42:D44)</f>
-        <v/>
-      </c>
-      <c r="E45" s="19">
-        <f>SUM(E42:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="19">
-        <f>SUM(F42:F44)</f>
-        <v/>
-      </c>
-      <c r="G45" s="19">
-        <f>SUM(G42:G44)</f>
-        <v/>
-      </c>
-      <c r="H45" s="19">
-        <f>SUM(H42:H44)</f>
-        <v/>
-      </c>
-      <c r="I45" s="19">
-        <f>SUM(I42:I44)</f>
-        <v/>
-      </c>
-      <c r="J45" s="19">
-        <f>SUM(J42:J44)</f>
-        <v/>
-      </c>
-      <c r="K45" s="19">
-        <f>SUM(K42:K44)</f>
-        <v/>
-      </c>
-      <c r="L45" s="19">
-        <f>SUM(L42:L44)</f>
-        <v/>
-      </c>
-      <c r="M45" s="19">
-        <f>SUM(M42:M44)</f>
-        <v/>
-      </c>
-      <c r="N45" s="19">
-        <f>SUM(N42:N44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="B46" s="19">
+        <f>SUM(B43:B45)</f>
+        <v/>
+      </c>
+      <c r="C46" s="19">
+        <f>SUM(C43:C45)</f>
+        <v/>
+      </c>
+      <c r="D46" s="19">
+        <f>SUM(D43:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="19">
+        <f>SUM(E43:E45)</f>
+        <v/>
+      </c>
+      <c r="F46" s="19">
+        <f>SUM(F43:F45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="19">
+        <f>SUM(G43:G45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="19">
+        <f>SUM(H43:H45)</f>
+        <v/>
+      </c>
+      <c r="I46" s="19">
+        <f>SUM(I43:I45)</f>
+        <v/>
+      </c>
+      <c r="J46" s="19">
+        <f>SUM(J43:J45)</f>
+        <v/>
+      </c>
+      <c r="K46" s="19">
+        <f>SUM(K43:K45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="19">
+        <f>SUM(L43:L45)</f>
+        <v/>
+      </c>
+      <c r="M46" s="19">
+        <f>SUM(M43:M45)</f>
+        <v/>
+      </c>
+      <c r="N46" s="19">
+        <f>SUM(N43:N45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>財務収支 差額（収入－支出）</t>
         </is>
       </c>
-      <c r="B46" s="14">
-        <f>B41-B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="14">
-        <f>C41-C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="14">
-        <f>D41-D45</f>
-        <v/>
-      </c>
-      <c r="E46" s="14">
-        <f>E41-E45</f>
-        <v/>
-      </c>
-      <c r="F46" s="14">
-        <f>F41-F45</f>
-        <v/>
-      </c>
-      <c r="G46" s="14">
-        <f>G41-G45</f>
-        <v/>
-      </c>
-      <c r="H46" s="14">
-        <f>H41-H45</f>
-        <v/>
-      </c>
-      <c r="I46" s="14">
-        <f>I41-I45</f>
-        <v/>
-      </c>
-      <c r="J46" s="14">
-        <f>J41-J45</f>
-        <v/>
-      </c>
-      <c r="K46" s="14">
-        <f>K41-K45</f>
-        <v/>
-      </c>
-      <c r="L46" s="14">
-        <f>L41-L45</f>
-        <v/>
-      </c>
-      <c r="M46" s="14">
-        <f>M41-M45</f>
-        <v/>
-      </c>
-      <c r="N46" s="14">
-        <f>N41-N45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="B47" s="14">
+        <f>B42-B46</f>
+        <v/>
+      </c>
+      <c r="C47" s="14">
+        <f>C42-C46</f>
+        <v/>
+      </c>
+      <c r="D47" s="14">
+        <f>D42-D46</f>
+        <v/>
+      </c>
+      <c r="E47" s="14">
+        <f>E42-E46</f>
+        <v/>
+      </c>
+      <c r="F47" s="14">
+        <f>F42-F46</f>
+        <v/>
+      </c>
+      <c r="G47" s="14">
+        <f>G42-G46</f>
+        <v/>
+      </c>
+      <c r="H47" s="14">
+        <f>H42-H46</f>
+        <v/>
+      </c>
+      <c r="I47" s="14">
+        <f>I42-I46</f>
+        <v/>
+      </c>
+      <c r="J47" s="14">
+        <f>J42-J46</f>
+        <v/>
+      </c>
+      <c r="K47" s="14">
+        <f>K42-K46</f>
+        <v/>
+      </c>
+      <c r="L47" s="14">
+        <f>L42-L46</f>
+        <v/>
+      </c>
+      <c r="M47" s="14">
+        <f>M42-M46</f>
+        <v/>
+      </c>
+      <c r="N47" s="14">
+        <f>N42-N46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>翌月繰越（月末残高）</t>
         </is>
       </c>
-      <c r="B47" s="14">
-        <f>B8+B26+B36+B46</f>
-        <v/>
-      </c>
-      <c r="C47" s="14">
-        <f>C8+C26+C36+C46</f>
-        <v/>
-      </c>
-      <c r="D47" s="14">
-        <f>D8+D26+D36+D46</f>
-        <v/>
-      </c>
-      <c r="E47" s="14">
-        <f>E8+E26+E36+E46</f>
-        <v/>
-      </c>
-      <c r="F47" s="14">
-        <f>F8+F26+F36+F46</f>
-        <v/>
-      </c>
-      <c r="G47" s="14">
-        <f>G8+G26+G36+G46</f>
-        <v/>
-      </c>
-      <c r="H47" s="14">
-        <f>H8+H26+H36+H46</f>
-        <v/>
-      </c>
-      <c r="I47" s="14">
-        <f>I8+I26+I36+I46</f>
-        <v/>
-      </c>
-      <c r="J47" s="14">
-        <f>J8+J26+J36+J46</f>
-        <v/>
-      </c>
-      <c r="K47" s="14">
-        <f>K8+K26+K36+K46</f>
-        <v/>
-      </c>
-      <c r="L47" s="14">
-        <f>L8+L26+L36+L46</f>
-        <v/>
-      </c>
-      <c r="M47" s="14">
-        <f>M8+M26+M36+M46</f>
-        <v/>
-      </c>
-      <c r="N47" s="14">
-        <f>M47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="B48" s="14">
+        <f>B8+B27+B37+B47</f>
+        <v/>
+      </c>
+      <c r="C48" s="14">
+        <f>C8+C27+C37+C47</f>
+        <v/>
+      </c>
+      <c r="D48" s="14">
+        <f>D8+D27+D37+D47</f>
+        <v/>
+      </c>
+      <c r="E48" s="14">
+        <f>E8+E27+E37+E47</f>
+        <v/>
+      </c>
+      <c r="F48" s="14">
+        <f>F8+F27+F37+F47</f>
+        <v/>
+      </c>
+      <c r="G48" s="14">
+        <f>G8+G27+G37+G47</f>
+        <v/>
+      </c>
+      <c r="H48" s="14">
+        <f>H8+H27+H37+H47</f>
+        <v/>
+      </c>
+      <c r="I48" s="14">
+        <f>I8+I27+I37+I47</f>
+        <v/>
+      </c>
+      <c r="J48" s="14">
+        <f>J8+J27+J37+J47</f>
+        <v/>
+      </c>
+      <c r="K48" s="14">
+        <f>K8+K27+K37+K47</f>
+        <v/>
+      </c>
+      <c r="L48" s="14">
+        <f>L8+L27+L37+L47</f>
+        <v/>
+      </c>
+      <c r="M48" s="14">
+        <f>M8+M27+M37+M47</f>
+        <v/>
+      </c>
+      <c r="N48" s="14">
+        <f>M48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>残高判定</t>
         </is>
       </c>
-      <c r="B48" s="21">
-        <f>IF(B47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="C48" s="21">
-        <f>IF(C47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="D48" s="21">
-        <f>IF(D47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="E48" s="21">
-        <f>IF(E47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="F48" s="21">
-        <f>IF(F47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="G48" s="21">
-        <f>IF(G47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="H48" s="21">
-        <f>IF(H47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="I48" s="21">
-        <f>IF(I47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="J48" s="21">
-        <f>IF(J47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="K48" s="21">
-        <f>IF(K47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="L48" s="21">
-        <f>IF(L47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-      <c r="M48" s="21">
-        <f>IF(M47&lt;$B$4,"要注意","OK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+      <c r="B49" s="21">
+        <f>IF(B48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="C49" s="21">
+        <f>IF(C48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="D49" s="21">
+        <f>IF(D48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="E49" s="21">
+        <f>IF(E48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="F49" s="21">
+        <f>IF(F48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="G49" s="21">
+        <f>IF(G48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="H49" s="21">
+        <f>IF(H48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="I49" s="21">
+        <f>IF(I48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="J49" s="21">
+        <f>IF(J48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="K49" s="21">
+        <f>IF(K48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="L49" s="21">
+        <f>IF(L48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+      <c r="M49" s="21">
+        <f>IF(M48&lt;$B$4,"要注意","OK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>※B列（1か月目）の数値は記入例です。実際の数値に置き換えてください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B47:M48">
+  <conditionalFormatting sqref="B48:M49">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B$47&lt;$B$4</formula>
+      <formula>B$48&lt;$B$4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
